--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בניטה - אכאב בשקט קאבר</v>
+        <v>אביחי טהיא - אל נבקש קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410989&amp;sid=343b179fe8bb09f870415378e128ebb7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410990&amp;sid=ffec9639250a4b1c014231eebf5db17d</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-23</v>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בניטה - אכאב בשקט קאבר</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>רונן לוגסי - אבא יקר קאבר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410988&amp;sid=343b179fe8bb09f870415378e128ebb7</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>רונן לוגסי - אבא יקר קאבר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>קורל אמויאל - עכשיו אתה חוזר בחזרה קאבר</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410987&amp;sid=343b179fe8bb09f870415378e128ebb7</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-23</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים זמרים מתחילים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>קורל אמויאל - עכשיו אתה חוזר בחזרה קאבר</v>
+        <v>אביחי טהיא - אל נבקש קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-05-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים זמרים מתחילים/sites/mizrahit-emerging/2026-05-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אביחי טהיא - אל נבקש קאבר</v>
+        <v>טודיאל - חדר מסתובב קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=410990&amp;sid=ffec9639250a4b1c014231eebf5db17d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411086&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,430 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אביחי טהיא - אל נבקש קאבר</v>
+        <v>טודיאל - חדר מסתובב קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>רון דבוש - עיניים עצובות קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411082&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>רון דבוש - עיניים עצובות קאבר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נתי יהב - אחות קטנה קאבר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411081&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נתי יהב - אחות קטנה קאבר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>נריה שריה עדני - אהובתי קאבר</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411080&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>נריה שריה עדני - אהובתי קאבר</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מימון בן שושן - תני ללכת קאבר</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411079&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מימון בן שושן - תני ללכת קאבר</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מימון בן שושן - אהבה בת 20 קאבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411078&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מימון בן שושן - אהבה בת 20 קאבר</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>יהונתן גד נגר - רוקד עם הכאב קאבר</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411077&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>יהונתן גד נגר - רוקד עם הכאב קאבר</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>יאיר כהן - רעשים קאבר</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411076&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>יאיר כהן - רעשים קאבר</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>בן גורן - בואי בשלום קאבר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411075&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>בן גורן - בואי בשלום קאבר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אפיק מרחום - פרחים מנייר קאבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411074&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אפיק מרחום - פרחים מנייר קאבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אליאור איצקוביץ׳ כהן - אליך אלוהיי קאבר</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411073&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אליאור איצקוביץ׳ כהן - אליך אלוהיי קאבר</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אושר פלמן - מכל האהבות קאבר</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=26&amp;t=411072&amp;sid=a2805d0eef120780bc83b2d9fb62f497</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים זמרים מתחילים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אושר פלמן - מכל האהבות קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>